--- a/diseases/d047/2026-2029.xlsx
+++ b/diseases/d047/2026-2029.xlsx
@@ -1158,7 +1158,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7632,7 +7632,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -9388,7 +9388,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -9790,7 +9790,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11546,7 +11546,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11948,7 +11948,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12350,7 +12350,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12752,7 +12752,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13154,7 +13154,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13556,7 +13556,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">

--- a/diseases/d047/2026-2029.xlsx
+++ b/diseases/d047/2026-2029.xlsx
@@ -1158,7 +1158,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7632,7 +7632,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -9388,7 +9388,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -9790,7 +9790,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11546,7 +11546,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11948,7 +11948,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12350,7 +12350,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12752,7 +12752,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13154,7 +13154,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13556,7 +13556,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">

--- a/diseases/d047/2026-2029.xlsx
+++ b/diseases/d047/2026-2029.xlsx
@@ -13641,6 +13641,408 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>infectious-diarrhea</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>其他感染性腹泻病</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>7724</v>
+      </c>
+      <c r="O68" t="n">
+        <v>7724</v>
+      </c>
+      <c r="P68" t="n">
+        <v>7724</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6.309028140037978</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP68" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ68" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV68" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA68" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB68" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC68" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>infectious-diarrhea</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>其他感染性腹泻病</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>7724</v>
+      </c>
+      <c r="O69" t="n">
+        <v>7724</v>
+      </c>
+      <c r="P69" t="n">
+        <v>7724</v>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>Infectious gastroenteritis</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN69" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP69" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ69" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS69" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV69" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA69" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB69" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC69" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13674,7 +14076,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -13757,7 +14159,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
@@ -13767,7 +14169,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11">
@@ -13787,7 +14189,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13">
@@ -13819,7 +14221,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1463371</v>
+        <v>1471095</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d047/2026-2029.xlsx
+++ b/diseases/d047/2026-2029.xlsx
@@ -916,9 +916,6 @@
       <c r="P3" t="n">
         <v>3708</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>3.028725575253861</v>
       </c>
@@ -1168,7 +1165,7 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN4" t="b">
@@ -1570,7 +1567,7 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN6" t="b">
@@ -1972,7 +1969,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN8" t="b">
@@ -2374,7 +2371,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN10" t="b">
@@ -2924,7 +2921,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3326,7 +3323,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3728,7 +3725,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4130,7 +4127,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4680,7 +4677,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN22" t="b">
@@ -5082,7 +5079,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN24" t="b">
@@ -5484,7 +5481,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN26" t="b">
@@ -5886,7 +5883,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN28" t="b">
@@ -6288,7 +6285,7 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN30" t="b">
@@ -6838,7 +6835,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7240,7 +7237,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7642,7 +7639,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8044,7 +8041,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8594,7 +8591,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN42" t="b">
@@ -8996,7 +8993,7 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN44" t="b">
@@ -9398,7 +9395,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN46" t="b">
@@ -9800,7 +9797,7 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN48" t="b">
@@ -10202,7 +10199,7 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN50" t="b">
@@ -10500,9 +10497,6 @@
       <c r="P52" t="n">
         <v>11033</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>9.011847160673099</v>
       </c>
@@ -10752,7 +10746,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -10902,9 +10896,6 @@
       <c r="P54" t="n">
         <v>11140</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>9.099245660282635</v>
       </c>
@@ -11154,7 +11145,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11304,9 +11295,6 @@
       <c r="P56" t="n">
         <v>10722</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>8.757819745920147</v>
       </c>
@@ -11556,7 +11544,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -11706,9 +11694,6 @@
       <c r="P58" t="n">
         <v>10373</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>8.472753611679694</v>
       </c>
@@ -11958,7 +11943,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12108,9 +12093,6 @@
       <c r="P60" t="n">
         <v>10023</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>8.186870669031675</v>
       </c>
@@ -12360,7 +12342,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12510,9 +12492,6 @@
       <c r="P62" t="n">
         <v>9669</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>7.897720492753394</v>
       </c>
@@ -12762,7 +12741,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -12912,9 +12891,6 @@
       <c r="P64" t="n">
         <v>9015</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>7.363527794205384</v>
       </c>
@@ -13164,7 +13140,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13314,9 +13290,6 @@
       <c r="P66" t="n">
         <v>7206</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>5.885921384918912</v>
       </c>
@@ -13566,7 +13539,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -13716,9 +13689,6 @@
       <c r="P68" t="n">
         <v>7724</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>6.309028140037978</v>
       </c>
@@ -13968,7 +13938,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN69" t="b">

--- a/diseases/d047/2026-2029.xlsx
+++ b/diseases/d047/2026-2029.xlsx
@@ -14013,6 +14013,405 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>infectious-diarrhea</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>其他感染性腹泻病</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>7674</v>
+      </c>
+      <c r="O70" t="n">
+        <v>7674</v>
+      </c>
+      <c r="P70" t="n">
+        <v>7674</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6.26818771965969</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP70" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ70" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV70" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA70" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB70" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC70" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>infectious-diarrhea</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>其他感染性腹泻病</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>7674</v>
+      </c>
+      <c r="O71" t="n">
+        <v>7674</v>
+      </c>
+      <c r="P71" t="n">
+        <v>7674</v>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Infectious gastroenteritis</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN71" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP71" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ71" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV71" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA71" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB71" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC71" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14046,7 +14445,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -14129,7 +14528,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
@@ -14139,7 +14538,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11">
@@ -14159,7 +14558,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13">
@@ -14191,7 +14590,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1471095</v>
+        <v>1478769</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d047/2026-2029.xlsx
+++ b/diseases/d047/2026-2029.xlsx
@@ -12046,12 +12046,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -12076,7 +12076,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -12085,73 +12085,59 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>10023</v>
+        <v>145175</v>
       </c>
       <c r="O60" t="n">
-        <v>10023</v>
-      </c>
-      <c r="P60" t="n">
-        <v>10023</v>
+        <v>145175</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>8.186870669031675</v>
+        <v>10.27486392708582</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ60" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS60" t="inlineStr">
-        <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -12161,22 +12147,22 @@
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -12203,7 +12189,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -12255,98 +12241,23 @@
       <c r="P61" t="n">
         <v>10023</v>
       </c>
+      <c r="R61" t="n">
+        <v>8.186870669031675</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U61" t="inlineStr">
         <is>
           <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>Infectious gastroenteritis</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>sentinel_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>sentinel_surveillance</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD61" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE61" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF61" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG61" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI61" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN61" t="b">
-        <v>1</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -12440,7 +12351,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12475,7 +12386,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -12484,31 +12395,106 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>9669</v>
+        <v>10023</v>
       </c>
       <c r="O62" t="n">
-        <v>9669</v>
+        <v>10023</v>
       </c>
       <c r="P62" t="n">
-        <v>9669</v>
-      </c>
-      <c r="R62" t="n">
-        <v>7.897720492753394</v>
-      </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>10023</v>
       </c>
       <c r="U62" t="inlineStr">
         <is>
           <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
         </is>
       </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Infectious gastroenteritis</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN62" t="b">
+        <v>1</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -12602,7 +12588,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12654,98 +12640,23 @@
       <c r="P63" t="n">
         <v>9669</v>
       </c>
+      <c r="R63" t="n">
+        <v>7.897720492753394</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U63" t="inlineStr">
         <is>
           <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
         </is>
       </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>Infectious gastroenteritis</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>sentinel_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>sentinel_surveillance</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD63" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE63" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF63" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG63" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN63" t="b">
-        <v>1</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -12839,7 +12750,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12874,7 +12785,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -12883,31 +12794,106 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>9015</v>
+        <v>9669</v>
       </c>
       <c r="O64" t="n">
-        <v>9015</v>
+        <v>9669</v>
       </c>
       <c r="P64" t="n">
-        <v>9015</v>
-      </c>
-      <c r="R64" t="n">
-        <v>7.363527794205384</v>
-      </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>9669</v>
       </c>
       <c r="U64" t="inlineStr">
         <is>
           <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
         </is>
       </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Infectious gastroenteritis</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN64" t="b">
+        <v>1</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -13001,7 +12987,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -13053,98 +13039,23 @@
       <c r="P65" t="n">
         <v>9015</v>
       </c>
+      <c r="R65" t="n">
+        <v>7.363527794205384</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U65" t="inlineStr">
         <is>
           <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
         </is>
       </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>Infectious gastroenteritis</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>sentinel_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>sentinel_surveillance</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD65" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE65" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF65" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG65" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
-        </is>
-      </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN65" t="b">
-        <v>1</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -13238,7 +13149,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -13273,7 +13184,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -13282,31 +13193,106 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>7206</v>
+        <v>9015</v>
       </c>
       <c r="O66" t="n">
-        <v>7206</v>
+        <v>9015</v>
       </c>
       <c r="P66" t="n">
-        <v>7206</v>
-      </c>
-      <c r="R66" t="n">
-        <v>5.885921384918912</v>
-      </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>9015</v>
       </c>
       <c r="U66" t="inlineStr">
         <is>
           <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
         </is>
       </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Infectious gastroenteritis</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG66" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN66" t="b">
+        <v>1</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -13400,7 +13386,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -13452,98 +13438,23 @@
       <c r="P67" t="n">
         <v>7206</v>
       </c>
+      <c r="R67" t="n">
+        <v>5.885921384918912</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U67" t="inlineStr">
         <is>
           <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
         </is>
       </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X67" t="inlineStr">
-        <is>
-          <t>Infectious gastroenteritis</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>sentinel_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>sentinel_surveillance</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD67" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE67" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF67" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG67" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN67" t="b">
-        <v>1</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -13637,7 +13548,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13672,40 +13583,115 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N68" t="n">
-        <v>7724</v>
+        <v>7206</v>
       </c>
       <c r="O68" t="n">
-        <v>7724</v>
+        <v>7206</v>
       </c>
       <c r="P68" t="n">
-        <v>7724</v>
-      </c>
-      <c r="R68" t="n">
-        <v>6.309028140037978</v>
-      </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>7206</v>
       </c>
       <c r="U68" t="inlineStr">
         <is>
           <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
         </is>
       </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Infectious gastroenteritis</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG68" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN68" t="b">
+        <v>1</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -13799,7 +13785,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13851,98 +13837,23 @@
       <c r="P69" t="n">
         <v>7724</v>
       </c>
+      <c r="R69" t="n">
+        <v>6.309028140037978</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U69" t="inlineStr">
         <is>
           <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
         </is>
       </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X69" t="inlineStr">
-        <is>
-          <t>Infectious gastroenteritis</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>sentinel_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>sentinel_surveillance</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD69" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE69" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF69" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG69" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN69" t="b">
-        <v>1</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -14036,7 +13947,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -14071,7 +13982,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -14080,31 +13991,106 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>7674</v>
+        <v>7724</v>
       </c>
       <c r="O70" t="n">
-        <v>7674</v>
+        <v>7724</v>
       </c>
       <c r="P70" t="n">
-        <v>7674</v>
-      </c>
-      <c r="R70" t="n">
-        <v>6.26818771965969</v>
-      </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>7724</v>
       </c>
       <c r="U70" t="inlineStr">
         <is>
           <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
         </is>
       </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>Infectious gastroenteritis</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE70" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF70" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG70" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN70" t="b">
+        <v>1</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -14198,7 +14184,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -14250,98 +14236,23 @@
       <c r="P71" t="n">
         <v>7674</v>
       </c>
+      <c r="R71" t="n">
+        <v>6.26818771965969</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U71" t="inlineStr">
         <is>
           <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
         </is>
       </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>Infectious gastroenteritis</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>sentinel_case_notifications</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>sentinel_surveillance</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD71" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE71" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF71" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG71" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
-        </is>
-      </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN71" t="b">
-        <v>1</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -14407,6 +14318,243 @@
         </is>
       </c>
       <c r="BC71" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>infectious-diarrhea</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>其他感染性腹泻病</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>7674</v>
+      </c>
+      <c r="O72" t="n">
+        <v>7674</v>
+      </c>
+      <c r="P72" t="n">
+        <v>7674</v>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Infectious gastroenteritis</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG72" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
+        </is>
+      </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN72" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP72" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ72" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV72" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA72" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB72" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC72" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -14528,7 +14676,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10">
@@ -14538,7 +14686,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11">
@@ -14590,7 +14738,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1478769</v>
+        <v>1623944</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d047/2026-2029.xlsx
+++ b/diseases/d047/2026-2029.xlsx
@@ -14560,6 +14560,405 @@
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>infectious-diarrhea</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>其他感染性腹泻病</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>4432</v>
+      </c>
+      <c r="O73" t="n">
+        <v>4432</v>
+      </c>
+      <c r="P73" t="n">
+        <v>4432</v>
+      </c>
+      <c r="R73" t="n">
+        <v>3.620094862331476</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP73" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ73" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV73" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA73" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB73" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC73" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>infectious-diarrhea</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>其他感染性腹泻病</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>4432</v>
+      </c>
+      <c r="O74" t="n">
+        <v>4432</v>
+      </c>
+      <c r="P74" t="n">
+        <v>4432</v>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Infectious gastroenteritis</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG74" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN74" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP74" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ74" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV74" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA74" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB74" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC74" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14593,7 +14992,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -14676,7 +15075,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10">
@@ -14686,7 +15085,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11">
@@ -14706,7 +15105,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13">
@@ -14738,7 +15137,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1623944</v>
+        <v>1628376</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d047/2026-2029.xlsx
+++ b/diseases/d047/2026-2029.xlsx
@@ -1155,7 +1155,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5069,7 +5069,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7227,7 +7227,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -9385,7 +9385,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -9787,7 +9787,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10189,7 +10189,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11135,7 +11135,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11534,7 +11534,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11933,7 +11933,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12480,7 +12480,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
@@ -12879,7 +12879,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -13278,7 +13278,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -13677,7 +13677,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -14076,7 +14076,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -14475,7 +14475,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">

--- a/diseases/d047/2026-2029.xlsx
+++ b/diseases/d047/2026-2029.xlsx
@@ -1155,7 +1155,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5069,7 +5069,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7227,7 +7227,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -9385,7 +9385,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -9787,7 +9787,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10189,7 +10189,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11135,7 +11135,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11534,7 +11534,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11933,7 +11933,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12480,7 +12480,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
@@ -12879,7 +12879,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -13278,7 +13278,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -13677,7 +13677,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -14076,7 +14076,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -14475,7 +14475,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">

--- a/diseases/d047/2026-2029.xlsx
+++ b/diseases/d047/2026-2029.xlsx
@@ -1155,7 +1155,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5069,7 +5069,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7227,7 +7227,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -9385,7 +9385,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -9787,7 +9787,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10189,7 +10189,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11135,7 +11135,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11534,7 +11534,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11933,7 +11933,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12480,7 +12480,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
@@ -12879,7 +12879,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -13278,7 +13278,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -13677,7 +13677,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -14076,7 +14076,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -14475,7 +14475,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">

--- a/diseases/d047/2026-2029.xlsx
+++ b/diseases/d047/2026-2029.xlsx
@@ -37674,6 +37674,405 @@
         </is>
       </c>
     </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>infectious-diarrhea</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>其他感染性腹泻病</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N193" t="n">
+        <v>7284</v>
+      </c>
+      <c r="O193" t="n">
+        <v>7284</v>
+      </c>
+      <c r="P193" t="n">
+        <v>7284</v>
+      </c>
+      <c r="R193" t="n">
+        <v>5.949632440709042</v>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO193" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP193" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ193" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS193" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT193" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU193" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV193" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW193" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX193" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY193" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA193" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB193" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC193" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>infectious-diarrhea</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>D047</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Infectious Diarrhea</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>其他感染性腹泻病</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N194" t="n">
+        <v>7284</v>
+      </c>
+      <c r="O194" t="n">
+        <v>7284</v>
+      </c>
+      <c r="P194" t="n">
+        <v>7284</v>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X194" t="inlineStr">
+        <is>
+          <t>Infectious gastroenteritis</t>
+        </is>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>sentinel_case_notifications</t>
+        </is>
+      </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>sentinel_surveillance</t>
+        </is>
+      </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB194" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD194" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE194" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF194" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG194" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH194" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI194" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ194" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK194" t="inlineStr">
+        <is>
+          <t>Japan NIID infectious gastroenteritis sentinel series without a specified etiology.</t>
+        </is>
+      </c>
+      <c r="AM194" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN194" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO194" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP194" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ194" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS194" t="inlineStr">
+        <is>
+          <t>SER_JP_INFECTIOUS_GASTROENTERITIS_SENTINEL_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT194" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU194" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV194" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW194" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX194" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY194" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA194" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB194" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC194" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -37707,7 +38106,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
@@ -37790,7 +38189,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -37800,7 +38199,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11">
@@ -37820,7 +38219,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -37852,7 +38251,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2186776</v>
+        <v>2194060</v>
       </c>
     </row>
     <row r="16">
